--- a/results/vwcpaper_appendixA.xlsx
+++ b/results/vwcpaper_appendixA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://365tno-my.sharepoint.com/personal/iris_eekhout_tno_nl/Documents/Documents/GitHub/dscoreddi/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_B8923127C2492CD4FE2735FA5F3D01CE821A9982" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35D0622D-3021-45B8-9AA2-79F6747A5673}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_B99231279E69E9C7D4C723FA5F3D01FDE2DC8AC0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59CB13DD-70AF-4619-95E8-EC495C7EC120}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-2025" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,11 +20,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="90">
   <si>
     <t>Ontwikkelingskenmerk</t>
   </si>
   <si>
+    <t>Van Wiechen-schema leeftijd in maanden</t>
+  </si>
+  <si>
     <t>domein</t>
   </si>
   <si>
@@ -43,278 +46,258 @@
     <t>P98</t>
   </si>
   <si>
-    <t>Reageert op toespreken (M)</t>
+    <t>1. Ogen fixeren</t>
+  </si>
+  <si>
+    <t>Fijne motoriek</t>
+  </si>
+  <si>
+    <t>2. Volgt met ogen en hoofd</t>
+  </si>
+  <si>
+    <t>3. Handen af en toe openen</t>
+  </si>
+  <si>
+    <t>4. Kijkt naar eigen handen</t>
+  </si>
+  <si>
+    <t>5. Speelt met handen middenvoor</t>
+  </si>
+  <si>
+    <t>6. Pakt in rugligging voorwerp binnen bereik</t>
+  </si>
+  <si>
+    <t>9. Speelt met beide voeten</t>
+  </si>
+  <si>
+    <t>7. Pakt blokje over</t>
+  </si>
+  <si>
+    <t>8. Houdt blokje vast, pakt er nog een in andere hand</t>
+  </si>
+  <si>
+    <t>10. Pakt propje met duim en wijsvinger</t>
+  </si>
+  <si>
+    <t>11. Doet blokje in/uit doos</t>
+  </si>
+  <si>
+    <t>12. Speelt geven en nemen (M)</t>
+  </si>
+  <si>
+    <t>14. Gaat op onderzoek uit (M)</t>
+  </si>
+  <si>
+    <t>16. Doet anderen na (M)</t>
+  </si>
+  <si>
+    <t>13. Stapelt 2 blokjes - rl</t>
+  </si>
+  <si>
+    <t>15. Stapelt 3 blokjes - rl</t>
+  </si>
+  <si>
+    <t>18. Plaatst ronde vorm in stoof</t>
+  </si>
+  <si>
+    <t>19. Trekt kledingstuk uit (M)</t>
+  </si>
+  <si>
+    <t>17. Stapelt 6 blokjes</t>
+  </si>
+  <si>
+    <t>21. Plaatst 3 vormen in stoof</t>
+  </si>
+  <si>
+    <t>22. Tekent verticale lijn na</t>
+  </si>
+  <si>
+    <t>20. Bouwt vrachtauto na</t>
+  </si>
+  <si>
+    <t>25. Trekt eigen kledingstuk aan (M)</t>
+  </si>
+  <si>
+    <t>23. Bouwt brug na</t>
+  </si>
+  <si>
+    <t>24. Plaatst 4 vormen in stoof</t>
+  </si>
+  <si>
+    <t>27. Houdt potlood met vingers vast</t>
+  </si>
+  <si>
+    <t>26. Tekent cirkel na</t>
+  </si>
+  <si>
+    <t>28*. Tekent kruis na</t>
+  </si>
+  <si>
+    <t>29. Reageert op toespreken (M)</t>
   </si>
   <si>
     <t>Communicatie</t>
   </si>
   <si>
-    <t>Lacht terug (M)</t>
-  </si>
-  <si>
-    <t>Maakt geluiden terug (M)</t>
-  </si>
-  <si>
-    <t>Maakt gevarieerde geluiden (M)</t>
-  </si>
-  <si>
-    <t>Draait hoofd naar geluid</t>
-  </si>
-  <si>
-    <t>Zegt dada-baba of gaga (M)</t>
-  </si>
-  <si>
-    <t>Brabbelt bij zijn spel (M)</t>
-  </si>
-  <si>
-    <t>Maakt communicatieve gebaren (M)</t>
-  </si>
-  <si>
-    <t>Reageert op mondeling verzoek (M)</t>
-  </si>
-  <si>
-    <t>Zegt 2 geluidswoorden met begrip (M)</t>
-  </si>
-  <si>
-    <t>Begrijpt enkele dagelijks gebruikte zinnen</t>
-  </si>
-  <si>
-    <t>Zegt 3 woorden met begrip (M)</t>
-  </si>
-  <si>
-    <t>Herkent twee objecten die genoemd worden</t>
-  </si>
-  <si>
-    <t>Begrijpt fantasieopdrachtjes (M)</t>
-  </si>
-  <si>
-    <t>Wijst 6 lichaamsdelen aan bij pop (M)</t>
-  </si>
-  <si>
-    <t>Zegt zinnen van 2 woorden (M)</t>
-  </si>
-  <si>
-    <t>Noemt zichzelf mij of ik  (M)</t>
-  </si>
-  <si>
-    <t>Is verstaanbaar voor bekenden (M)</t>
-  </si>
-  <si>
-    <t>Wijst 5 plaatjes aan in boek</t>
-  </si>
-  <si>
-    <t>Zegt “zinnen” van 3 of meer woorden (M)</t>
-  </si>
-  <si>
-    <t>Stelt vragen naar “wie”, “wat”, “waar”, “hoe” (M)</t>
-  </si>
-  <si>
-    <t>Is goed verstaanbaar voor onderzoeker</t>
-  </si>
-  <si>
-    <t>Praat spontaan over gebeurtenissen thuis/speelzaal (M)</t>
-  </si>
-  <si>
-    <t>Stelt vragen naar “hoeveel”, “wanneer”, “waarom” (M)</t>
-  </si>
-  <si>
-    <t>Begrijpt analogieën en tegenstellingen (M)</t>
-  </si>
-  <si>
-    <t>Ogen fixeren</t>
-  </si>
-  <si>
-    <t>Fijne motoriek</t>
-  </si>
-  <si>
-    <t>Volgt met ogen en hoofd</t>
-  </si>
-  <si>
-    <t>Handen af en toe openen</t>
-  </si>
-  <si>
-    <t>Kijkt naar eigen handen</t>
-  </si>
-  <si>
-    <t>Speelt met handen middenvoor</t>
-  </si>
-  <si>
-    <t>Pakt in rugligging voorwerp binnen bereik</t>
-  </si>
-  <si>
-    <t>Speelt met beide voeten</t>
-  </si>
-  <si>
-    <t>Pakt blokje over</t>
-  </si>
-  <si>
-    <t>Houdt blokje vast, pakt er nog een in andere hand</t>
-  </si>
-  <si>
-    <t>Pakt propje met duim en wijsvinger</t>
-  </si>
-  <si>
-    <t>Doet blokje in/uit doos</t>
-  </si>
-  <si>
-    <t>Speelt geven en nemen (M)</t>
-  </si>
-  <si>
-    <t>Gaat op onderzoek uit (M)</t>
-  </si>
-  <si>
-    <t>Doet anderen na (M)</t>
-  </si>
-  <si>
-    <t>Stapelt 2 blokjes - rl</t>
-  </si>
-  <si>
-    <t>Eet zelf met lepel (M)</t>
-  </si>
-  <si>
-    <t>Stapelt 3 blokjes - rl</t>
-  </si>
-  <si>
-    <t>Plaatst ronde vorm in stoof</t>
-  </si>
-  <si>
-    <t>Trekt kledingstuk uit (M)</t>
-  </si>
-  <si>
-    <t>Stapelt 6 blokjes</t>
-  </si>
-  <si>
-    <t>Plaatst 3 vormen in stoof</t>
-  </si>
-  <si>
-    <t>Tekent verticale lijn na</t>
-  </si>
-  <si>
-    <t>Bouwt vrachtauto na</t>
-  </si>
-  <si>
-    <t>Trekt eigen kledingstuk aan (M)</t>
-  </si>
-  <si>
-    <t>Bouwt brug na</t>
-  </si>
-  <si>
-    <t>Plaatst 4 vormen in stoof</t>
-  </si>
-  <si>
-    <t>Houdt potlood met vingers vast</t>
-  </si>
-  <si>
-    <t>Tekent cirkel na</t>
-  </si>
-  <si>
-    <t>Tekent kruis na</t>
-  </si>
-  <si>
-    <t>Beweegt armen evenveel - rl</t>
+    <t>30. Lacht terug (M)</t>
+  </si>
+  <si>
+    <t>31. Maakt geluiden terug (M)</t>
+  </si>
+  <si>
+    <t>32*. Maakt gevarieerde geluiden (M)</t>
+  </si>
+  <si>
+    <t>33. Zegt dada-baba of gaga (M)</t>
+  </si>
+  <si>
+    <t>34. Brabbelt bij zijn spel (M)</t>
+  </si>
+  <si>
+    <t>36. Maakt communicatieve gebaren (M)</t>
+  </si>
+  <si>
+    <t>35. Reageert op mondeling verzoek (M)</t>
+  </si>
+  <si>
+    <t>38*. Begrijpt enkele dagelijks gebruikte zinnen</t>
+  </si>
+  <si>
+    <t>37. Zegt 2 geluidswoorden met begrip (M)</t>
+  </si>
+  <si>
+    <t>40*. Begrijpt fantasieopdrachtjes (M)</t>
+  </si>
+  <si>
+    <t>39. Zegt 3 woorden met begrip (M)</t>
+  </si>
+  <si>
+    <t>42. Wijst 6 lichaamsdelen aan bij pop (M)</t>
+  </si>
+  <si>
+    <t>41. Zegt zinnen van 2 woorden (M)</t>
+  </si>
+  <si>
+    <t>43. Noemt zichzelf mij of ik  (M)</t>
+  </si>
+  <si>
+    <t>46. Is verstaanbaar voor bekenden (M)</t>
+  </si>
+  <si>
+    <t>44. Wijst 5 plaatjes aan in boek</t>
+  </si>
+  <si>
+    <t>45. Zegt “zinnen” van 3 of meer woorden (M)</t>
+  </si>
+  <si>
+    <t>48. Stelt vragen naar “wie”, “wat”, “waar”, “hoe” (M)</t>
+  </si>
+  <si>
+    <t>49. Is goed verstaanbaar voor onderzoeker</t>
+  </si>
+  <si>
+    <t>47. Praat spontaan over gebeurtenissen thuis/speelzaal (M)</t>
+  </si>
+  <si>
+    <t>50. Stelt vragen naar “hoeveel”, “wanneer”, “waarom” (M)</t>
+  </si>
+  <si>
+    <t>51*. Begrijpt analogieën en tegenstellingen (M)</t>
+  </si>
+  <si>
+    <t>52. Beweegt armen evenveel - rl</t>
   </si>
   <si>
     <t>Grove motoriek</t>
   </si>
   <si>
-    <t>Beweegt benen evenveel - rl</t>
-  </si>
-  <si>
-    <t>Heft kin even van onderlaag</t>
-  </si>
-  <si>
-    <t>Blijft hangen bij optillen onder de oksels</t>
-  </si>
-  <si>
-    <t>Heft in buikligging hoofd tot 45º</t>
-  </si>
-  <si>
-    <t>Benen gebogen of trappelen bij verticaal zwaaien - rl</t>
-  </si>
-  <si>
-    <t>Reacties bij optrekken tot zit</t>
-  </si>
-  <si>
-    <t>Kijkt rond met 90º geheven hoofd</t>
-  </si>
-  <si>
-    <t>Kan hoofd goed ophouden in zit</t>
-  </si>
-  <si>
-    <t>Rolt zich om van rug naar buik en omgekeerd (M)</t>
-  </si>
-  <si>
-    <t>Zit op billen met gestrekte benen</t>
-  </si>
-  <si>
-    <t>Zit stabiel los</t>
-  </si>
-  <si>
-    <t>Kruipt vooruit, buik op de grond (M)</t>
-  </si>
-  <si>
-    <t>Trekt zich op tot staan</t>
-  </si>
-  <si>
-    <t>Kruipt, buik vrij van de grond (M)</t>
-  </si>
-  <si>
-    <t>Loopt langs (M)</t>
-  </si>
-  <si>
-    <t>Loopt los</t>
-  </si>
-  <si>
-    <t>Kan hurken en weer gaan staan zonder steun en zonder hulp van anderen</t>
-  </si>
-  <si>
-    <t>Loopt goed los</t>
-  </si>
-  <si>
-    <t>Gooit bal zonder om te vallen</t>
-  </si>
-  <si>
-    <t>Drinkt uit beker</t>
-  </si>
-  <si>
-    <t>Kan in zit soepel roteren</t>
-  </si>
-  <si>
-    <t>Loopt soepel</t>
-  </si>
-  <si>
-    <t>Schopt bal weg - rl</t>
-  </si>
-  <si>
-    <t>Springt met beide voeten tegelijk</t>
-  </si>
-  <si>
-    <t>Fietst (op driewieler) (M)</t>
-  </si>
-  <si>
-    <t>Kan minstens 5 seconden op een been staan - rl</t>
-  </si>
-  <si>
-    <t>Note: (M) geeft aan dat dit kenmerk ook op basis van mededeling gescoord mag worden; "rl" geeft aan dat zowel rechts als links bekeken moet worden</t>
-  </si>
-  <si>
-    <t>Van Wiechen-schema leeftijd in maanden</t>
+    <t>53. Beweegt benen evenveel - rl</t>
+  </si>
+  <si>
+    <t>54. Blijft hangen bij optillen onder de oksels</t>
+  </si>
+  <si>
+    <t>55. Reacties bij optrekken tot zit</t>
+  </si>
+  <si>
+    <t>56. Heft kin even van onderlaag</t>
+  </si>
+  <si>
+    <t>57. Heft in buikligging hoofd tot 45º</t>
+  </si>
+  <si>
+    <t>59. Benen gebogen of trappelen bij verticaal zwaaien - rl</t>
+  </si>
+  <si>
+    <t>58. Kijkt rond met 90º geheven hoofd</t>
+  </si>
+  <si>
+    <t>61. Kan hoofd goed ophouden in zit</t>
+  </si>
+  <si>
+    <t>60. Rolt zich om van rug naar buik en omgekeerd (M)</t>
+  </si>
+  <si>
+    <t>62. Zit op billen met gestrekte benen</t>
+  </si>
+  <si>
+    <t>63. Zit stabiel los</t>
+  </si>
+  <si>
+    <t>64. Kruipt vooruit, buik op de grond (M)</t>
+  </si>
+  <si>
+    <t>65. Trekt zich op tot staan</t>
+  </si>
+  <si>
+    <t>66. Kruipt, buik vrij van de grond (M)</t>
+  </si>
+  <si>
+    <t>67. Loopt langs (M)</t>
+  </si>
+  <si>
+    <t>68.1. Loopt los</t>
+  </si>
+  <si>
+    <t>70. Kan hurken en weer gaan staan zonder steun en zonder hulp van anderen</t>
+  </si>
+  <si>
+    <t>68.2. Loopt goed los</t>
+  </si>
+  <si>
+    <t>69. Gooit bal zonder om te vallen</t>
+  </si>
+  <si>
+    <t>72. Kan in zit soepel roteren</t>
+  </si>
+  <si>
+    <t>68.3. Loopt soepel</t>
+  </si>
+  <si>
+    <t>71. Schopt bal weg - rl</t>
+  </si>
+  <si>
+    <t>74. Springt met beide voeten tegelijk</t>
+  </si>
+  <si>
+    <t>73. Fietst (op driewieler) (M)</t>
+  </si>
+  <si>
+    <t>75*. Kan minstens 5 seconden op een been staan - rl</t>
+  </si>
+  <si>
+    <t>Note: *Percentielen van deze kenmerken zijn erbij geschat, omdat hier nog geen D-score van bekend is; (M) geeft aan dat dit kenmerk ook op basis van mededeling gescoord mag worden; "rl" geeft aan dat zowel rechts als links bekeken moet worden; -- deze kenmerken worden gedurende het eerste jaar herhaaldelijk afgenomen.</t>
+  </si>
+  <si>
+    <t>`--`</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -362,10 +345,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -663,48 +645,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="50.90625" customWidth="1"/>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
+    <col min="1" max="1" width="46.1796875" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -713,663 +696,663 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G2">
-        <v>0.17</v>
+        <v>0.62</v>
       </c>
       <c r="H2">
-        <v>0.6</v>
+        <v>1.1100000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="E3">
-        <v>0.21</v>
+        <v>0.6</v>
       </c>
       <c r="F3">
-        <v>0.79</v>
+        <v>1.25</v>
       </c>
       <c r="G3">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>2.0699999999999998</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>0.17</v>
+        <v>0.4</v>
       </c>
       <c r="E4">
-        <v>0.6</v>
+        <v>0.87</v>
       </c>
       <c r="F4">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="H4">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>1.65</v>
+        <v>0.96</v>
       </c>
       <c r="E5">
-        <v>2.2799999999999998</v>
+        <v>1.49</v>
       </c>
       <c r="F5">
-        <v>3.23</v>
+        <v>2.29</v>
       </c>
       <c r="G5">
-        <v>4.37</v>
+        <v>3.24</v>
       </c>
       <c r="H5">
-        <v>5.41</v>
+        <v>4.1100000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>2.73</v>
+        <v>2.17</v>
       </c>
       <c r="E6">
-        <v>3.52</v>
+        <v>2.87</v>
       </c>
       <c r="F6">
-        <v>4.71</v>
+        <v>3.94</v>
       </c>
       <c r="G6">
-        <v>6.15</v>
+        <v>5.22</v>
       </c>
       <c r="H6">
-        <v>7.45</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>3.84</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="E7">
-        <v>4.8</v>
+        <v>3.24</v>
       </c>
       <c r="F7">
-        <v>6.25</v>
+        <v>4.38</v>
       </c>
       <c r="G7">
-        <v>7.99</v>
+        <v>5.75</v>
       </c>
       <c r="H7">
-        <v>9.5500000000000007</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8">
-        <v>5.19</v>
+        <v>3.18</v>
       </c>
       <c r="E8">
-        <v>6.35</v>
+        <v>4.04</v>
       </c>
       <c r="F8">
-        <v>8.1</v>
+        <v>5.34</v>
       </c>
       <c r="G8">
-        <v>10.199999999999999</v>
+        <v>6.89</v>
       </c>
       <c r="H8">
-        <v>12.09</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9">
-        <v>5.89</v>
+        <v>3.84</v>
       </c>
       <c r="E9">
-        <v>7.15</v>
+        <v>4.8</v>
       </c>
       <c r="F9">
-        <v>9.0500000000000007</v>
+        <v>6.25</v>
       </c>
       <c r="G9">
-        <v>11.34</v>
+        <v>7.99</v>
       </c>
       <c r="H9">
-        <v>13.41</v>
+        <v>9.5500000000000007</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10">
-        <v>6.79</v>
+        <v>3.97</v>
       </c>
       <c r="E10">
-        <v>8.18</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="F10">
-        <v>10.29</v>
+        <v>6.42</v>
       </c>
       <c r="G10">
-        <v>12.82</v>
+        <v>8.19</v>
       </c>
       <c r="H10">
-        <v>15.13</v>
+        <v>9.7899999999999991</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>8.5399999999999991</v>
+        <v>5.89</v>
       </c>
       <c r="E11">
-        <v>10.18</v>
+        <v>7.15</v>
       </c>
       <c r="F11">
-        <v>12.69</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="G11">
-        <v>15.74</v>
+        <v>11.34</v>
       </c>
       <c r="H11">
-        <v>18.579999999999998</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12">
-        <v>9.39</v>
+        <v>6.9</v>
       </c>
       <c r="E12">
-        <v>11.16</v>
+        <v>8.31</v>
       </c>
       <c r="F12">
-        <v>13.87</v>
+        <v>10.44</v>
       </c>
       <c r="G12">
-        <v>17.2</v>
+        <v>13</v>
       </c>
       <c r="H12">
-        <v>20.3</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13">
-        <v>9.9600000000000009</v>
+        <v>7.09</v>
       </c>
       <c r="E13">
-        <v>11.82</v>
+        <v>8.52</v>
       </c>
       <c r="F13">
-        <v>14.67</v>
+        <v>10.7</v>
       </c>
       <c r="G13">
-        <v>18.18</v>
+        <v>13.31</v>
       </c>
       <c r="H13">
-        <v>21.47</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14">
-        <v>11.07</v>
+        <v>7.24</v>
       </c>
       <c r="E14">
-        <v>13.11</v>
+        <v>8.69</v>
       </c>
       <c r="F14">
-        <v>16.25</v>
+        <v>10.9</v>
       </c>
       <c r="G14">
-        <v>20.149999999999999</v>
+        <v>13.56</v>
       </c>
       <c r="H14">
-        <v>23.78</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15">
-        <v>12.41</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="E15">
-        <v>14.66</v>
+        <v>11.32</v>
       </c>
       <c r="F15">
-        <v>18.170000000000002</v>
+        <v>14.07</v>
       </c>
       <c r="G15">
-        <v>22.53</v>
+        <v>17.43</v>
       </c>
       <c r="H15">
-        <v>26.55</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16">
-        <v>12.65</v>
+        <v>11.62</v>
       </c>
       <c r="E16">
-        <v>14.93</v>
+        <v>13.73</v>
       </c>
       <c r="F16">
-        <v>18.52</v>
+        <v>17.03</v>
       </c>
       <c r="G16">
-        <v>22.96</v>
+        <v>21.11</v>
       </c>
       <c r="H16">
-        <v>27.04</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17">
-        <v>13.89</v>
+        <v>13.26</v>
       </c>
       <c r="E17">
-        <v>16.39</v>
+        <v>15.64</v>
       </c>
       <c r="F17">
-        <v>20.32</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="G17">
-        <v>25.18</v>
+        <v>24.04</v>
       </c>
       <c r="H17">
-        <v>29.62</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18">
-        <v>14.89</v>
+        <v>13.95</v>
       </c>
       <c r="E18">
-        <v>17.57</v>
+        <v>16.47</v>
       </c>
       <c r="F18">
-        <v>21.8</v>
+        <v>20.420000000000002</v>
       </c>
       <c r="G18">
-        <v>26.97</v>
+        <v>25.29</v>
       </c>
       <c r="H18">
-        <v>31.68</v>
+        <v>29.75</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19">
-        <v>14.96</v>
+        <v>14.15</v>
       </c>
       <c r="E19">
-        <v>17.66</v>
+        <v>16.7</v>
       </c>
       <c r="F19">
-        <v>21.9</v>
+        <v>20.71</v>
       </c>
       <c r="G19">
-        <v>27.09</v>
+        <v>25.65</v>
       </c>
       <c r="H19">
-        <v>31.83</v>
+        <v>30.16</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20">
-        <v>15.24</v>
+        <v>15.53</v>
       </c>
       <c r="E20">
-        <v>17.989999999999998</v>
+        <v>18.329999999999998</v>
       </c>
       <c r="F20">
-        <v>22.31</v>
+        <v>22.73</v>
       </c>
       <c r="G20">
-        <v>27.59</v>
+        <v>28.1</v>
       </c>
       <c r="H20">
-        <v>32.4</v>
+        <v>32.979999999999997</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21">
         <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21">
-        <v>16.04</v>
+        <v>17.37</v>
       </c>
       <c r="E21">
-        <v>18.940000000000001</v>
+        <v>20.5</v>
       </c>
       <c r="F21">
-        <v>23.48</v>
+        <v>25.39</v>
       </c>
       <c r="G21">
-        <v>29.01</v>
+        <v>31.31</v>
       </c>
       <c r="H21">
-        <v>34.159999999999997</v>
+        <v>37.200000000000003</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22">
-        <v>18.37</v>
+        <v>18.54</v>
       </c>
       <c r="E22">
-        <v>21.68</v>
+        <v>21.89</v>
       </c>
       <c r="F22">
-        <v>26.83</v>
+        <v>27.08</v>
       </c>
       <c r="G22">
-        <v>33.049999999999997</v>
+        <v>33.340000000000003</v>
       </c>
       <c r="H22">
-        <v>39.39</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23">
-        <v>18.8</v>
+        <v>19.61</v>
       </c>
       <c r="E23">
-        <v>22.19</v>
+        <v>23.14</v>
       </c>
       <c r="F23">
-        <v>27.44</v>
+        <v>28.59</v>
       </c>
       <c r="G23">
-        <v>33.869999999999997</v>
+        <v>35.479999999999997</v>
       </c>
       <c r="H23">
-        <v>40.369999999999997</v>
+        <v>42.19</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24">
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24">
-        <v>18.98</v>
+        <v>19.61</v>
       </c>
       <c r="E24">
-        <v>22.4</v>
+        <v>23.14</v>
       </c>
       <c r="F24">
-        <v>27.7</v>
+        <v>28.59</v>
       </c>
       <c r="G24">
-        <v>34.229999999999997</v>
+        <v>35.479999999999997</v>
       </c>
       <c r="H24">
-        <v>40.76</v>
+        <v>42.19</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25">
-        <v>21.42</v>
+        <v>20.84</v>
       </c>
       <c r="E25">
-        <v>25.26</v>
+        <v>24.57</v>
       </c>
       <c r="F25">
-        <v>31.16</v>
+        <v>30.33</v>
       </c>
       <c r="G25">
-        <v>38.9</v>
+        <v>37.81</v>
       </c>
       <c r="H25">
-        <v>46.39</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26">
-        <v>26.37</v>
+        <v>20.84</v>
       </c>
       <c r="E26">
-        <v>31</v>
+        <v>24.57</v>
       </c>
       <c r="F26">
-        <v>38.69</v>
+        <v>30.33</v>
       </c>
       <c r="G26">
-        <v>48.67</v>
+        <v>37.81</v>
       </c>
       <c r="H26">
-        <v>58.74</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>20.93</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>24.68</v>
       </c>
       <c r="F27">
-        <v>0.06</v>
+        <v>30.47</v>
       </c>
       <c r="G27">
-        <v>0.62</v>
+        <v>37.979999999999997</v>
       </c>
       <c r="H27">
-        <v>1.1100000000000001</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
@@ -1377,25 +1360,25 @@
         <v>35</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D28">
-        <v>0.17</v>
+        <v>21.83</v>
       </c>
       <c r="E28">
-        <v>0.6</v>
+        <v>25.73</v>
       </c>
       <c r="F28">
-        <v>1.25</v>
+        <v>31.72</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>39.67</v>
       </c>
       <c r="H28">
-        <v>2.68</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
@@ -1403,25 +1386,25 @@
         <v>36</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>0.4</v>
+        <v>24.06</v>
       </c>
       <c r="E29">
-        <v>0.87</v>
+        <v>28.32</v>
       </c>
       <c r="F29">
-        <v>1.56</v>
+        <v>35.1</v>
       </c>
       <c r="G29">
-        <v>2.37</v>
+        <v>43.99</v>
       </c>
       <c r="H29">
-        <v>3.1</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
@@ -1429,114 +1412,114 @@
         <v>37</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D30">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>3.24</v>
+        <v>0.17</v>
       </c>
       <c r="H30">
-        <v>4.1100000000000003</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+      <c r="C31" t="s">
         <v>38</v>
       </c>
-      <c r="B31">
-        <v>6</v>
-      </c>
-      <c r="C31" t="s">
-        <v>34</v>
-      </c>
       <c r="D31">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>2.87</v>
+        <v>0.21</v>
       </c>
       <c r="F31">
-        <v>3.94</v>
+        <v>0.79</v>
       </c>
       <c r="G31">
-        <v>5.22</v>
+        <v>1.46</v>
       </c>
       <c r="H31">
-        <v>6.38</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D32">
-        <v>2.4900000000000002</v>
+        <v>0.17</v>
       </c>
       <c r="E32">
-        <v>3.24</v>
+        <v>0.6</v>
       </c>
       <c r="F32">
-        <v>4.38</v>
+        <v>1.25</v>
       </c>
       <c r="G32">
-        <v>5.75</v>
+        <v>2</v>
       </c>
       <c r="H32">
-        <v>6.99</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D33">
-        <v>3.18</v>
+        <v>1.65</v>
       </c>
       <c r="E33">
-        <v>4.04</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="F33">
-        <v>5.34</v>
+        <v>3.23</v>
       </c>
       <c r="G33">
-        <v>6.89</v>
+        <v>4.37</v>
       </c>
       <c r="H33">
-        <v>8.3000000000000007</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34">
         <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D34">
         <v>3.84</v>
@@ -1556,39 +1539,39 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D35">
-        <v>3.97</v>
+        <v>5.19</v>
       </c>
       <c r="E35">
-        <v>4.9400000000000004</v>
+        <v>6.35</v>
       </c>
       <c r="F35">
-        <v>6.42</v>
+        <v>8.1</v>
       </c>
       <c r="G35">
-        <v>8.19</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="H35">
-        <v>9.7899999999999991</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B36">
         <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D36">
         <v>5.89</v>
@@ -1608,533 +1591,473 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B37">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D37">
-        <v>6.9</v>
+        <v>6.79</v>
       </c>
       <c r="E37">
-        <v>8.31</v>
+        <v>8.18</v>
       </c>
       <c r="F37">
-        <v>10.44</v>
+        <v>10.29</v>
       </c>
       <c r="G37">
-        <v>13</v>
+        <v>12.82</v>
       </c>
       <c r="H37">
-        <v>15.35</v>
+        <v>15.13</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B38">
         <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D38">
-        <v>7.09</v>
+        <v>7.28</v>
       </c>
       <c r="E38">
-        <v>8.52</v>
+        <v>8.74</v>
       </c>
       <c r="F38">
-        <v>10.7</v>
+        <v>10.96</v>
       </c>
       <c r="G38">
-        <v>13.31</v>
+        <v>13.62</v>
       </c>
       <c r="H38">
-        <v>15.71</v>
+        <v>16.079999999999998</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B39">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D39">
-        <v>7.24</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="E39">
-        <v>8.69</v>
+        <v>10.18</v>
       </c>
       <c r="F39">
-        <v>10.9</v>
+        <v>12.69</v>
       </c>
       <c r="G39">
-        <v>13.56</v>
+        <v>15.74</v>
       </c>
       <c r="H39">
-        <v>16</v>
+        <v>18.579999999999998</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B40">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D40">
-        <v>9.5299999999999994</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="E40">
-        <v>11.32</v>
+        <v>10.18</v>
       </c>
       <c r="F40">
-        <v>14.07</v>
+        <v>12.69</v>
       </c>
       <c r="G40">
-        <v>17.43</v>
+        <v>15.74</v>
       </c>
       <c r="H40">
-        <v>20.59</v>
+        <v>18.579999999999998</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B41">
         <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D41">
-        <v>11.62</v>
+        <v>9.9600000000000009</v>
       </c>
       <c r="E41">
-        <v>13.73</v>
+        <v>11.82</v>
       </c>
       <c r="F41">
-        <v>17.03</v>
+        <v>14.67</v>
       </c>
       <c r="G41">
-        <v>21.11</v>
+        <v>18.18</v>
       </c>
       <c r="H41">
-        <v>24.9</v>
+        <v>21.47</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B42">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D42">
-        <v>12.83</v>
+        <v>12.65</v>
       </c>
       <c r="E42">
-        <v>15.14</v>
+        <v>14.93</v>
       </c>
       <c r="F42">
-        <v>18.78</v>
+        <v>18.52</v>
       </c>
       <c r="G42">
-        <v>23.28</v>
+        <v>22.96</v>
       </c>
       <c r="H42">
-        <v>27.41</v>
+        <v>27.04</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B43">
         <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D43">
-        <v>13.26</v>
+        <v>13.89</v>
       </c>
       <c r="E43">
-        <v>15.64</v>
+        <v>16.39</v>
       </c>
       <c r="F43">
-        <v>19.399999999999999</v>
+        <v>20.32</v>
       </c>
       <c r="G43">
-        <v>24.04</v>
+        <v>25.18</v>
       </c>
       <c r="H43">
-        <v>28.3</v>
+        <v>29.62</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B44">
         <v>30</v>
       </c>
       <c r="C44" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D44">
-        <v>13.95</v>
+        <v>14.89</v>
       </c>
       <c r="E44">
-        <v>16.47</v>
+        <v>17.57</v>
       </c>
       <c r="F44">
-        <v>20.420000000000002</v>
+        <v>21.8</v>
       </c>
       <c r="G44">
-        <v>25.29</v>
+        <v>26.97</v>
       </c>
       <c r="H44">
-        <v>29.75</v>
+        <v>31.68</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B45">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C45" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D45">
-        <v>14.15</v>
+        <v>14.96</v>
       </c>
       <c r="E45">
-        <v>16.7</v>
+        <v>17.66</v>
       </c>
       <c r="F45">
-        <v>20.71</v>
+        <v>21.9</v>
       </c>
       <c r="G45">
-        <v>25.65</v>
+        <v>27.09</v>
       </c>
       <c r="H45">
-        <v>30.16</v>
+        <v>31.83</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B46">
         <v>30</v>
       </c>
       <c r="C46" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D46">
-        <v>15.53</v>
+        <v>15.24</v>
       </c>
       <c r="E46">
-        <v>18.329999999999998</v>
+        <v>17.989999999999998</v>
       </c>
       <c r="F46">
-        <v>22.73</v>
+        <v>22.31</v>
       </c>
       <c r="G46">
-        <v>28.1</v>
+        <v>27.59</v>
       </c>
       <c r="H46">
-        <v>32.979999999999997</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B47">
         <v>36</v>
       </c>
       <c r="C47" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D47">
-        <v>17.37</v>
+        <v>16.04</v>
       </c>
       <c r="E47">
-        <v>20.5</v>
+        <v>18.940000000000001</v>
       </c>
       <c r="F47">
-        <v>25.39</v>
+        <v>23.48</v>
       </c>
       <c r="G47">
-        <v>31.31</v>
+        <v>29.01</v>
       </c>
       <c r="H47">
-        <v>37.200000000000003</v>
+        <v>34.159999999999997</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B48">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C48" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D48">
-        <v>18.54</v>
+        <v>18.37</v>
       </c>
       <c r="E48">
-        <v>21.89</v>
+        <v>21.68</v>
       </c>
       <c r="F48">
-        <v>27.08</v>
+        <v>26.83</v>
       </c>
       <c r="G48">
-        <v>33.340000000000003</v>
+        <v>33.049999999999997</v>
       </c>
       <c r="H48">
-        <v>39.78</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B49">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C49" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D49">
-        <v>19.61</v>
+        <v>18.8</v>
       </c>
       <c r="E49">
-        <v>23.14</v>
+        <v>22.19</v>
       </c>
       <c r="F49">
-        <v>28.59</v>
+        <v>27.44</v>
       </c>
       <c r="G49">
-        <v>35.479999999999997</v>
+        <v>33.869999999999997</v>
       </c>
       <c r="H49">
-        <v>42.19</v>
+        <v>40.369999999999997</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B50">
         <v>42</v>
       </c>
       <c r="C50" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D50">
-        <v>19.61</v>
+        <v>18.98</v>
       </c>
       <c r="E50">
-        <v>23.14</v>
+        <v>22.4</v>
       </c>
       <c r="F50">
-        <v>28.59</v>
+        <v>27.7</v>
       </c>
       <c r="G50">
-        <v>35.479999999999997</v>
+        <v>34.229999999999997</v>
       </c>
       <c r="H50">
-        <v>42.19</v>
+        <v>40.76</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B51">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D51">
-        <v>20.84</v>
+        <v>21.42</v>
       </c>
       <c r="E51">
-        <v>24.57</v>
+        <v>25.26</v>
       </c>
       <c r="F51">
-        <v>30.33</v>
+        <v>31.16</v>
       </c>
       <c r="G51">
-        <v>37.81</v>
+        <v>38.9</v>
       </c>
       <c r="H51">
-        <v>45.01</v>
+        <v>46.39</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B52">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C52" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D52">
-        <v>20.84</v>
+        <v>26.37</v>
       </c>
       <c r="E52">
-        <v>24.57</v>
+        <v>31</v>
       </c>
       <c r="F52">
-        <v>30.33</v>
+        <v>38.69</v>
       </c>
       <c r="G52">
-        <v>37.81</v>
+        <v>48.67</v>
       </c>
       <c r="H52">
-        <v>45.01</v>
+        <v>58.74</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53">
-        <v>48</v>
+        <v>61</v>
+      </c>
+      <c r="B53" t="s">
+        <v>89</v>
       </c>
       <c r="C53" t="s">
-        <v>34</v>
-      </c>
-      <c r="D53">
-        <v>20.93</v>
-      </c>
-      <c r="E53">
-        <v>24.68</v>
-      </c>
-      <c r="F53">
-        <v>30.47</v>
-      </c>
-      <c r="G53">
-        <v>37.979999999999997</v>
-      </c>
-      <c r="H53">
-        <v>45.24</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54">
-        <v>48</v>
+        <v>63</v>
+      </c>
+      <c r="B54" t="s">
+        <v>89</v>
       </c>
       <c r="C54" t="s">
-        <v>34</v>
-      </c>
-      <c r="D54">
-        <v>21.83</v>
-      </c>
-      <c r="E54">
-        <v>25.73</v>
-      </c>
-      <c r="F54">
-        <v>31.72</v>
-      </c>
-      <c r="G54">
-        <v>39.67</v>
-      </c>
-      <c r="H54">
-        <v>47.34</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>64</v>
+      </c>
+      <c r="B55" t="s">
+        <v>89</v>
+      </c>
+      <c r="C55" t="s">
         <v>62</v>
-      </c>
-      <c r="B55">
-        <v>54</v>
-      </c>
-      <c r="C55" t="s">
-        <v>34</v>
-      </c>
-      <c r="D55">
-        <v>24.06</v>
-      </c>
-      <c r="E55">
-        <v>28.32</v>
-      </c>
-      <c r="F55">
-        <v>35.1</v>
-      </c>
-      <c r="G55">
-        <v>43.99</v>
-      </c>
-      <c r="H55">
-        <v>52.77</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56">
-        <v>1</v>
+        <v>65</v>
+      </c>
+      <c r="B56" t="s">
+        <v>89</v>
       </c>
       <c r="C56" t="s">
-        <v>64</v>
-      </c>
-      <c r="D56">
-        <v>0</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
-      <c r="H56">
-        <v>0.13</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2143,672 +2066,568 @@
         <v>0</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="H57">
-        <v>0.16</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C58" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="F58">
-        <v>0.04</v>
+        <v>2.16</v>
       </c>
       <c r="G58">
-        <v>0.59</v>
+        <v>3.09</v>
       </c>
       <c r="H58">
-        <v>1.08</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D59">
-        <v>0.32</v>
+        <v>1.73</v>
       </c>
       <c r="E59">
-        <v>0.77</v>
+        <v>2.36</v>
       </c>
       <c r="F59">
-        <v>1.45</v>
+        <v>3.33</v>
       </c>
       <c r="G59">
-        <v>2.2400000000000002</v>
+        <v>4.49</v>
       </c>
       <c r="H59">
-        <v>2.95</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D60">
-        <v>0.86</v>
+        <v>2.09</v>
       </c>
       <c r="E60">
-        <v>1.38</v>
+        <v>2.78</v>
       </c>
       <c r="F60">
-        <v>2.16</v>
+        <v>3.84</v>
       </c>
       <c r="G60">
-        <v>3.09</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="H60">
-        <v>3.93</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B61">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D61">
-        <v>1.73</v>
+        <v>3.03</v>
       </c>
       <c r="E61">
-        <v>2.36</v>
+        <v>3.86</v>
       </c>
       <c r="F61">
-        <v>3.33</v>
+        <v>5.12</v>
       </c>
       <c r="G61">
-        <v>4.49</v>
+        <v>6.64</v>
       </c>
       <c r="H61">
-        <v>5.55</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B62">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D62">
-        <v>1.78</v>
+        <v>3.53</v>
       </c>
       <c r="E62">
-        <v>2.42</v>
+        <v>4.43</v>
       </c>
       <c r="F62">
-        <v>3.4</v>
+        <v>5.81</v>
       </c>
       <c r="G62">
-        <v>4.58</v>
+        <v>7.47</v>
       </c>
       <c r="H62">
-        <v>5.64</v>
+        <v>8.9499999999999993</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B63">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D63">
-        <v>2.09</v>
+        <v>3.57</v>
       </c>
       <c r="E63">
-        <v>2.78</v>
+        <v>4.49</v>
       </c>
       <c r="F63">
-        <v>3.84</v>
+        <v>5.88</v>
       </c>
       <c r="G63">
-        <v>5.0999999999999996</v>
+        <v>7.54</v>
       </c>
       <c r="H63">
-        <v>6.24</v>
+        <v>9.0399999999999991</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B64">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D64">
-        <v>3.03</v>
+        <v>4.92</v>
       </c>
       <c r="E64">
-        <v>3.86</v>
+        <v>6.04</v>
       </c>
       <c r="F64">
-        <v>5.12</v>
+        <v>7.74</v>
       </c>
       <c r="G64">
-        <v>6.64</v>
+        <v>9.76</v>
       </c>
       <c r="H64">
-        <v>8.01</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B65">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D65">
-        <v>3.53</v>
+        <v>5.89</v>
       </c>
       <c r="E65">
-        <v>4.43</v>
+        <v>7.15</v>
       </c>
       <c r="F65">
-        <v>5.81</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="G65">
-        <v>7.47</v>
+        <v>11.34</v>
       </c>
       <c r="H65">
-        <v>8.9499999999999993</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B66">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D66">
-        <v>3.57</v>
+        <v>6.29</v>
       </c>
       <c r="E66">
-        <v>4.49</v>
+        <v>7.61</v>
       </c>
       <c r="F66">
-        <v>5.88</v>
+        <v>9.61</v>
       </c>
       <c r="G66">
-        <v>7.54</v>
+        <v>12</v>
       </c>
       <c r="H66">
-        <v>9.0399999999999991</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B67">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C67" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D67">
-        <v>4.92</v>
+        <v>6.94</v>
       </c>
       <c r="E67">
-        <v>6.04</v>
+        <v>8.35</v>
       </c>
       <c r="F67">
-        <v>7.74</v>
+        <v>10.49</v>
       </c>
       <c r="G67">
-        <v>9.76</v>
+        <v>13.06</v>
       </c>
       <c r="H67">
-        <v>11.59</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B68">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C68" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D68">
-        <v>5.89</v>
+        <v>6.94</v>
       </c>
       <c r="E68">
-        <v>7.15</v>
+        <v>8.35</v>
       </c>
       <c r="F68">
-        <v>9.0500000000000007</v>
+        <v>10.49</v>
       </c>
       <c r="G68">
-        <v>11.34</v>
+        <v>13.06</v>
       </c>
       <c r="H68">
-        <v>13.41</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B69">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C69" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D69">
-        <v>6.29</v>
+        <v>9.34</v>
       </c>
       <c r="E69">
-        <v>7.61</v>
+        <v>11.11</v>
       </c>
       <c r="F69">
-        <v>9.61</v>
+        <v>13.81</v>
       </c>
       <c r="G69">
-        <v>12</v>
+        <v>17.12</v>
       </c>
       <c r="H69">
-        <v>14.18</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B70">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C70" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D70">
-        <v>6.94</v>
+        <v>11.02</v>
       </c>
       <c r="E70">
-        <v>8.35</v>
+        <v>13.05</v>
       </c>
       <c r="F70">
-        <v>10.49</v>
+        <v>16.170000000000002</v>
       </c>
       <c r="G70">
-        <v>13.06</v>
+        <v>20.059999999999999</v>
       </c>
       <c r="H70">
-        <v>15.42</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B71">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C71" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D71">
-        <v>6.94</v>
+        <v>11.13</v>
       </c>
       <c r="E71">
-        <v>8.35</v>
+        <v>13.17</v>
       </c>
       <c r="F71">
-        <v>10.49</v>
+        <v>16.329999999999998</v>
       </c>
       <c r="G71">
-        <v>13.06</v>
+        <v>20.239999999999998</v>
       </c>
       <c r="H71">
-        <v>15.42</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B72">
         <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D72">
-        <v>9.34</v>
+        <v>11.4</v>
       </c>
       <c r="E72">
-        <v>11.11</v>
+        <v>13.48</v>
       </c>
       <c r="F72">
-        <v>13.81</v>
+        <v>16.71</v>
       </c>
       <c r="G72">
-        <v>17.12</v>
+        <v>20.72</v>
       </c>
       <c r="H72">
-        <v>20.2</v>
+        <v>24.45</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B73">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C73" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D73">
-        <v>11.02</v>
+        <v>13.76</v>
       </c>
       <c r="E73">
-        <v>13.05</v>
+        <v>16.239999999999998</v>
       </c>
       <c r="F73">
-        <v>16.170000000000002</v>
+        <v>20.14</v>
       </c>
       <c r="G73">
-        <v>20.059999999999999</v>
+        <v>24.95</v>
       </c>
       <c r="H73">
-        <v>23.67</v>
+        <v>29.35</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B74">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C74" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D74">
-        <v>11.13</v>
+        <v>14.96</v>
       </c>
       <c r="E74">
-        <v>13.17</v>
+        <v>17.66</v>
       </c>
       <c r="F74">
-        <v>16.329999999999998</v>
+        <v>21.9</v>
       </c>
       <c r="G74">
-        <v>20.239999999999998</v>
+        <v>27.09</v>
       </c>
       <c r="H74">
-        <v>23.89</v>
+        <v>31.83</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B75">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C75" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D75">
-        <v>11.4</v>
+        <v>16.73</v>
       </c>
       <c r="E75">
-        <v>13.48</v>
+        <v>19.760000000000002</v>
       </c>
       <c r="F75">
-        <v>16.71</v>
+        <v>24.48</v>
       </c>
       <c r="G75">
-        <v>20.72</v>
+        <v>30.21</v>
       </c>
       <c r="H75">
-        <v>24.45</v>
+        <v>35.770000000000003</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B76">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C76" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D76">
-        <v>12.83</v>
+        <v>18.71</v>
       </c>
       <c r="E76">
-        <v>15.14</v>
+        <v>22.09</v>
       </c>
       <c r="F76">
-        <v>18.78</v>
+        <v>27.32</v>
       </c>
       <c r="G76">
-        <v>23.28</v>
+        <v>33.69</v>
       </c>
       <c r="H76">
-        <v>27.41</v>
+        <v>40.17</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B77">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C77" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D77">
-        <v>13.76</v>
+        <v>19.16</v>
       </c>
       <c r="E77">
-        <v>16.239999999999998</v>
+        <v>22.61</v>
       </c>
       <c r="F77">
-        <v>20.14</v>
+        <v>27.96</v>
       </c>
       <c r="G77">
-        <v>24.95</v>
+        <v>34.590000000000003</v>
       </c>
       <c r="H77">
-        <v>29.35</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>86</v>
-      </c>
-      <c r="B78">
-        <v>36</v>
-      </c>
-      <c r="C78" t="s">
-        <v>64</v>
-      </c>
-      <c r="D78">
-        <v>14.96</v>
-      </c>
-      <c r="E78">
-        <v>17.66</v>
-      </c>
-      <c r="F78">
-        <v>21.9</v>
-      </c>
-      <c r="G78">
-        <v>27.09</v>
-      </c>
-      <c r="H78">
-        <v>31.83</v>
+      <c r="A78" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B78" s="1">
+        <v>54</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D78" s="1">
+        <v>24.06</v>
+      </c>
+      <c r="E78" s="1">
+        <v>28.32</v>
+      </c>
+      <c r="F78" s="1">
+        <v>35.1</v>
+      </c>
+      <c r="G78" s="1">
+        <v>43.99</v>
+      </c>
+      <c r="H78" s="1">
+        <v>52.77</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>87</v>
-      </c>
-      <c r="B79">
-        <v>30</v>
-      </c>
-      <c r="C79" t="s">
-        <v>64</v>
-      </c>
-      <c r="D79">
-        <v>16.73</v>
-      </c>
-      <c r="E79">
-        <v>19.760000000000002</v>
-      </c>
-      <c r="F79">
-        <v>24.48</v>
-      </c>
-      <c r="G79">
-        <v>30.21</v>
-      </c>
-      <c r="H79">
-        <v>35.770000000000003</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
         <v>88</v>
-      </c>
-      <c r="B80">
-        <v>42</v>
-      </c>
-      <c r="C80" t="s">
-        <v>64</v>
-      </c>
-      <c r="D80">
-        <v>18.71</v>
-      </c>
-      <c r="E80">
-        <v>22.09</v>
-      </c>
-      <c r="F80">
-        <v>27.32</v>
-      </c>
-      <c r="G80">
-        <v>33.69</v>
-      </c>
-      <c r="H80">
-        <v>40.17</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>89</v>
-      </c>
-      <c r="B81">
-        <v>36</v>
-      </c>
-      <c r="C81" t="s">
-        <v>64</v>
-      </c>
-      <c r="D81">
-        <v>19.16</v>
-      </c>
-      <c r="E81">
-        <v>22.61</v>
-      </c>
-      <c r="F81">
-        <v>27.96</v>
-      </c>
-      <c r="G81">
-        <v>34.590000000000003</v>
-      </c>
-      <c r="H81">
-        <v>41.17</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A82" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B82" s="1">
-        <v>54</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D82" s="1">
-        <v>24.06</v>
-      </c>
-      <c r="E82" s="1">
-        <v>28.32</v>
-      </c>
-      <c r="F82" s="1">
-        <v>35.1</v>
-      </c>
-      <c r="G82" s="1">
-        <v>43.99</v>
-      </c>
-      <c r="H82" s="1">
-        <v>52.77</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A83" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>